--- a/testdata/searchData.xlsx
+++ b/testdata/searchData.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wasim\Downloads\amazon-selenium\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD37328-3C34-4847-B8A8-F29953B55B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D06D041-ABD1-4C29-8AF0-67B2049A57A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -921,4 +926,49 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60573BF-049B-4F54-AEE3-31DC17BAC0AE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB61A642-4F19-458B-9C47-B49C89775A50}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7724C90-ECA9-46C4-81DB-B70AAD8B90DB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C628AD4A-6578-4A3F-A0F0-24734687F9DA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDD6434-60B8-46CF-97EB-0526D6C21F4B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>